--- a/backtest_runs/20260410_193731/by_symbol/AGTL/AGTL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AGTL/AGTL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1163.760000000006</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100854.88</v>
@@ -679,7 +679,7 @@
         <v>-8430.239999999994</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92424.63999999998</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>95641.35999999999</v>
@@ -817,7 +817,7 @@
         <v>-1335.360000000009</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>94305.99999999999</v>
@@ -863,7 +863,7 @@
         <v>-455.5199999999936</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>93850.47999999998</v>
@@ -909,7 +909,7 @@
         <v>-464.8800000000028</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>93385.59999999999</v>
@@ -1001,7 +1001,7 @@
         <v>-218.3999999999965</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>94349.67999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-274.5599999999986</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>94075.12</v>
@@ -1139,7 +1139,7 @@
         <v>-839.2799999999993</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>94365.27999999998</v>
@@ -1185,7 +1185,7 @@
         <v>-6.239999999994325</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>94359.03999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-1347.839999999998</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>93011.19999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-1906.320000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>91104.87999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-1163.759999999988</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>89941.12</v>
@@ -1415,7 +1415,7 @@
         <v>-1513.199999999989</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>90902.07999999999</v>
